--- a/Data/Home/LivingRoom.Heater001.xlsx
+++ b/Data/Home/LivingRoom.Heater001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,159 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Heater_Operation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1712401791</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LivingRoom.Heater001.state: on</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Heater_Operation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1712403215</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LivingRoom.Heater001.state: off</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Heater_Operation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1713614527</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LivingRoom.Heater001.state: on</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Heater_Operation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1713616109</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LivingRoom.Heater001.state: off</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
